--- a/6. Silabus/Komputer.xlsx
+++ b/6. Silabus/Komputer.xlsx
@@ -1,58 +1,576 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+  <si>
+    <t>SILABUS MATA PELAJARAN</t>
+  </si>
+  <si>
+    <t>NAMA MAPEL :</t>
+  </si>
+  <si>
+    <t>PRAKTIKUM KOMPUTER</t>
+  </si>
+  <si>
+    <t>PENYUSUN      :</t>
+  </si>
+  <si>
+    <t>Ustadz Muhammad Zaini, S.Psi.</t>
+  </si>
+  <si>
+    <t>SEMESTER 1</t>
+  </si>
+  <si>
+    <t>16 PERTEMUAN</t>
+  </si>
+  <si>
+    <t>Ustadz Abdul Latip, S.Pd.</t>
+  </si>
+  <si>
+    <t>SEMESTER 2</t>
+  </si>
+  <si>
+    <t>13 PERTEMUAN</t>
+  </si>
+  <si>
+    <t>KELAS</t>
+  </si>
+  <si>
+    <t>SEMESTER</t>
+  </si>
+  <si>
+    <t>TEMA</t>
+  </si>
+  <si>
+    <t>SUB TEMA</t>
+  </si>
+  <si>
+    <t>ALOKASI WAKTU</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>ULA</t>
+  </si>
+  <si>
+    <t>GANJIL</t>
+  </si>
+  <si>
+    <t>MENGETIK 10 JARI</t>
+  </si>
+  <si>
+    <t>MICROSOFT WORD</t>
+  </si>
+  <si>
+    <t>PENGATURAN PARAGRAF DAN TEKS</t>
+  </si>
+  <si>
+    <t>BULLET &amp; NUMBERING</t>
+  </si>
+  <si>
+    <t>TABULASI &amp; INDENTASI</t>
+  </si>
+  <si>
+    <t>KOLOM</t>
+  </si>
+  <si>
+    <t>GENAP</t>
+  </si>
+  <si>
+    <t>WORD ART &amp; TABLE</t>
+  </si>
+  <si>
+    <t>PENOMORAN OUTLINE</t>
+  </si>
+  <si>
+    <t>STRUKTUR ORGANISASI</t>
+  </si>
+  <si>
+    <t>DRAWING</t>
+  </si>
+  <si>
+    <t>MICROSOFT EXCEL</t>
+  </si>
+  <si>
+    <t>DATEDIF</t>
+  </si>
+  <si>
+    <t>DAYS TODAY</t>
+  </si>
+  <si>
+    <t>ALT =</t>
+  </si>
+  <si>
+    <t>VLOOKUP</t>
+  </si>
+  <si>
+    <t>TSANIYAH</t>
+  </si>
+  <si>
+    <t>PIVOT TABLE</t>
+  </si>
+  <si>
+    <t>TEXTJOIN</t>
+  </si>
+  <si>
+    <t>NOTA</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>CTRL E</t>
+  </si>
+  <si>
+    <t>EKSTRAK JUDUL &amp; TAHUN</t>
+  </si>
+  <si>
+    <t>CUSTOM FORMAT</t>
+  </si>
+  <si>
+    <t>RANK</t>
+  </si>
+  <si>
+    <t>MENGGABUNGKAN TEMPAT &amp; TANGGAL</t>
+  </si>
+  <si>
+    <t>MENGAMBIL NAMA TENGAH</t>
+  </si>
+  <si>
+    <t>WEBSITE</t>
+  </si>
+  <si>
+    <t>SKILL CAVEMAN</t>
+  </si>
+  <si>
+    <t>TIMEZONE</t>
+  </si>
+  <si>
+    <t>CHUNKING</t>
+  </si>
+  <si>
+    <t>FRONTEND</t>
+  </si>
+  <si>
+    <t>BACKEND</t>
+  </si>
+  <si>
+    <t>BUILD</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>PEMBAYARAN</t>
+  </si>
+  <si>
+    <t>DATABASE</t>
+  </si>
+  <si>
+    <t>WHATSAPP</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="General&quot;X&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -60,18 +578,358 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
+    <cellStyle name="Mata Uang" xfId="2" builtinId="4"/>
+    <cellStyle name="Persen" xfId="3" builtinId="5"/>
+    <cellStyle name="Koma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Mata Uang [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink yang Diikuti" xfId="7" builtinId="9"/>
+    <cellStyle name="Catatan" xfId="8" builtinId="10"/>
+    <cellStyle name="Teks Peringatan" xfId="9" builtinId="11"/>
+    <cellStyle name="Judul" xfId="10" builtinId="15"/>
+    <cellStyle name="Teks CExplanatory" xfId="11" builtinId="53"/>
+    <cellStyle name="Kepala 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Kepala 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Kepala 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Kepala 4" xfId="15" builtinId="19"/>
+    <cellStyle name="input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Perhitungan" xfId="18" builtinId="22"/>
+    <cellStyle name="Cek Sel" xfId="19" builtinId="23"/>
+    <cellStyle name="Sel Ditautkan" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Baik" xfId="22" builtinId="26"/>
+    <cellStyle name="Buruk" xfId="23" builtinId="27"/>
+    <cellStyle name="Netral" xfId="24" builtinId="28"/>
+    <cellStyle name="Aksen1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Aksen1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Aksen1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Aksen1" xfId="28" builtinId="32"/>
+    <cellStyle name="Aksen2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Aksen2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Aksen2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Aksen2" xfId="32" builtinId="36"/>
+    <cellStyle name="Aksen3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Aksen3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Aksen3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Aksen3" xfId="36" builtinId="40"/>
+    <cellStyle name="Aksen4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Aksen4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Aksen4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Aksen4" xfId="40" builtinId="44"/>
+    <cellStyle name="Aksen5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Aksen5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Aksen5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Aksen5" xfId="44" builtinId="48"/>
+    <cellStyle name="Aksen6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Aksen6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Aksen6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Aksen6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,22 +1249,614 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="14.6" customWidth="1"/>
+    <col min="2" max="2" width="29.6" customWidth="1"/>
+    <col min="3" max="3" width="18.1" customWidth="1"/>
+    <col min="4" max="4" width="38.7" customWidth="1"/>
+    <col min="5" max="5" width="16.2" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.9" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v/>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="10">
+        <v>8</v>
+      </c>
+      <c r="F8" s="11">
+        <f>E8</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11">
+        <f>F8+E9</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="11">
+        <f>F9+E10</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11">
+        <f>F10+E11</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="10">
+        <v>2</v>
+      </c>
+      <c r="F12" s="11">
+        <f>F11+E12</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="11">
+        <f>E13</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="10">
+        <v>2</v>
+      </c>
+      <c r="F14" s="11">
+        <f>F13+E14</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="11">
+        <f>F14+E15</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
+        <f>F15+E16</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11">
+        <f>F16+E17</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="10">
+        <v>2</v>
+      </c>
+      <c r="F18" s="11">
+        <f>F17+E18</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11">
+        <f>F18+E19</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2</v>
+      </c>
+      <c r="F20" s="11">
+        <f>F19+E20</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11">
+        <f>E21</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11">
+        <f>F21+E22</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11">
+        <f>F22+E23</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11">
+        <f>F23+E24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11">
+        <f>F24+E25</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11">
+        <f>F25+E26</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11">
+        <f>F26+E27</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11">
+        <f>F27+E28</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11">
+        <f>F28+E29</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11">
+        <f>F29+E30</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="10">
+        <v>2</v>
+      </c>
+      <c r="F31" s="11">
+        <f>F30+E31</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="10">
+        <v>2</v>
+      </c>
+      <c r="F32" s="11">
+        <f>F31+E32</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="10">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11">
+        <f>F32+E33</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2</v>
+      </c>
+      <c r="F34" s="11">
+        <f>E34</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" s="11">
+        <f>F34+E35</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2</v>
+      </c>
+      <c r="F36" s="11">
+        <f>F35+E36</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="10">
+        <v>2</v>
+      </c>
+      <c r="F37" s="11">
+        <f>F36+E37</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="10">
+        <v>2</v>
+      </c>
+      <c r="F38" s="11">
+        <f>F37+E38</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="10">
+        <v>2</v>
+      </c>
+      <c r="F39" s="11">
+        <f>F38+E39</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="10">
+        <v>2</v>
+      </c>
+      <c r="F40" s="11">
+        <f>F39+E40</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
+  <mergeCells count="10">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:A20"/>
+    <mergeCell ref="A21:A40"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B20"/>
+    <mergeCell ref="B21:B33"/>
+    <mergeCell ref="B34:B40"/>
+    <mergeCell ref="C9:C16"/>
+    <mergeCell ref="C17:C30"/>
+    <mergeCell ref="C31:C40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>